--- a/data/trans_dic/IP16A05-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A05-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos</t>
+          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 17,06</t>
+          <t>1,72; 16,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 38,73</t>
+          <t>10,05; 37,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,69</t>
+          <t>0,0; 14,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 19,65</t>
+          <t>2,17; 20,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 24,27</t>
+          <t>4,36; 24,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 27,45</t>
+          <t>7,26; 29,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,26; 32,79</t>
+          <t>6,0; 33,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,99</t>
+          <t>0,0; 10,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 17,05</t>
+          <t>3,69; 16,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,89; 28,07</t>
+          <t>10,51; 27,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 18,61</t>
+          <t>3,11; 18,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 12,04</t>
+          <t>1,24; 12,86</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,09; 22,41</t>
+          <t>6,04; 21,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 24,5</t>
+          <t>7,29; 25,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,16; 25,93</t>
+          <t>9,47; 27,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,07; 16,13</t>
+          <t>2,81; 15,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 16,99</t>
+          <t>2,96; 16,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,0; 29,08</t>
+          <t>8,22; 29,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 18,38</t>
+          <t>3,22; 17,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 16,51</t>
+          <t>2,79; 15,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 16,5</t>
+          <t>5,57; 16,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,34; 24,73</t>
+          <t>10,08; 24,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 19,55</t>
+          <t>7,94; 19,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 13,45</t>
+          <t>4,0; 13,75</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 18,81</t>
+          <t>2,04; 17,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,49; 28,74</t>
+          <t>8,18; 28,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 22,44</t>
+          <t>3,84; 23,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 23,23</t>
+          <t>2,13; 22,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,95; 21,92</t>
+          <t>5,13; 22,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 15,3</t>
+          <t>1,66; 15,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,33; 35,32</t>
+          <t>10,97; 36,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 13,75</t>
+          <t>2,57; 14,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 16,86</t>
+          <t>4,64; 16,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,79; 17,71</t>
+          <t>6,02; 18,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,94; 24,92</t>
+          <t>9,23; 24,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 17,14</t>
+          <t>3,56; 16,49</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 22,1</t>
+          <t>2,77; 22,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,48; 31,57</t>
+          <t>10,01; 31,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 26,31</t>
+          <t>5,16; 25,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 15,11</t>
+          <t>1,77; 16,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 21,31</t>
+          <t>4,26; 21,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 22,72</t>
+          <t>5,84; 23,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 19,93</t>
+          <t>2,3; 19,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,04</t>
+          <t>0,0; 10,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 17,55</t>
+          <t>4,43; 17,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,32; 23,88</t>
+          <t>10,04; 23,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 18,98</t>
+          <t>5,97; 19,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,06</t>
+          <t>0,88; 8,68</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 13,73</t>
+          <t>5,14; 13,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,88; 23,92</t>
+          <t>12,83; 23,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 16,59</t>
+          <t>7,72; 16,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 14,54</t>
+          <t>4,53; 14,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 15,09</t>
+          <t>6,8; 14,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,82; 18,12</t>
+          <t>8,86; 17,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,73; 18,77</t>
+          <t>8,27; 18,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,11</t>
+          <t>3,17; 9,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,83; 12,52</t>
+          <t>6,87; 12,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,25; 19,17</t>
+          <t>12,25; 19,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,44; 16,06</t>
+          <t>9,47; 16,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 10,42</t>
+          <t>4,72; 9,94</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2060</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6814</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3391</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5016</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3894</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5451</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11830</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2591</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>564; 5396</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3161; 11832</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3454</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>562; 5399</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1250; 7031</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2501; 10294</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1450; 8121</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2961</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2267; 10046</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6921; 18198</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1510; 8893</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>664; 6879</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5119</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5992</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7079</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3483</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3243</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7076</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3593</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4959</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>8361</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>13069</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10671</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>8442</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2516; 8978</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3024; 10609</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4042; 11595</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1244; 6910</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1223; 6738</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3313; 11984</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1327; 7309</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1780; 10083</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4625; 13534</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>8250; 19745</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>6659; 16042</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4323; 14857</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5487</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7874</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3870</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2284</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5827</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3495</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5674</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7770</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8830</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>11370</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>513; 4416</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2696; 9250</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1062; 6441</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1640; 17435</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1803; 7876</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>598; 5418</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3051; 10081</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1461; 8144</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2795; 9970</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4152; 12589</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5116; 13518</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4772; 22101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2173</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8082</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4209</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1686</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4178</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6089</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2744</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6352</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>14171</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6953</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>710; 5753</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4184; 13084</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1692; 8255</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>542; 5046</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1655; 8217</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2759; 11056</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>694; 5924</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3616</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2860; 11196</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>8936; 20483</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3759; 12143</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>568; 5588</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>11155</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26375</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14895</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15013</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14682</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20465</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>16058</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>9798</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>25837</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>46840</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>30953</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>24812</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>6445; 17141</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>18949; 34234</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9846; 21561</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8044; 25937</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9792; 21384</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13999; 28216</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10193; 23328</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>5777; 17076</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>18490; 34483</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>37430; 58313</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>23748; 40852</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>16992; 35777</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A05-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A05-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 16,44</t>
+          <t>1,71; 15,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,05; 37,63</t>
+          <t>9,83; 37,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,18</t>
+          <t>0,0; 11,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 20,89</t>
+          <t>2,15; 20,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 24,52</t>
+          <t>4,56; 25,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 29,9</t>
+          <t>6,26; 28,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 33,59</t>
+          <t>6,22; 34,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,71</t>
+          <t>0,0; 12,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 16,34</t>
+          <t>4,25; 16,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 27,63</t>
+          <t>10,29; 27,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 18,32</t>
+          <t>3,31; 18,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 12,86</t>
+          <t>1,21; 11,24</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,04; 21,56</t>
+          <t>4,73; 21,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 25,56</t>
+          <t>6,86; 25,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,47; 27,15</t>
+          <t>9,17; 27,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 15,62</t>
+          <t>3,06; 16,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 16,31</t>
+          <t>3,02; 16,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,22; 29,72</t>
+          <t>8,96; 30,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 17,76</t>
+          <t>3,22; 18,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 15,8</t>
+          <t>3,05; 17,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 16,32</t>
+          <t>5,48; 16,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,08; 24,13</t>
+          <t>9,98; 23,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,94; 19,13</t>
+          <t>7,91; 19,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 13,75</t>
+          <t>4,14; 13,16</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 17,55</t>
+          <t>2,06; 19,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,18; 28,06</t>
+          <t>8,35; 27,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 23,32</t>
+          <t>4,04; 23,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 22,62</t>
+          <t>2,43; 23,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 22,43</t>
+          <t>4,04; 22,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 15,05</t>
+          <t>1,69; 16,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,97; 36,25</t>
+          <t>10,85; 35,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 14,31</t>
+          <t>1,97; 15,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 16,54</t>
+          <t>4,62; 16,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 18,26</t>
+          <t>6,08; 18,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 24,39</t>
+          <t>9,29; 25,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 16,49</t>
+          <t>3,73; 16,12</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 22,41</t>
+          <t>2,78; 22,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,01; 31,31</t>
+          <t>10,96; 31,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 25,18</t>
+          <t>4,46; 24,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 16,51</t>
+          <t>1,73; 14,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 21,17</t>
+          <t>3,67; 21,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 23,41</t>
+          <t>6,02; 23,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 19,65</t>
+          <t>2,51; 20,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,7</t>
+          <t>0,0; 10,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 17,36</t>
+          <t>4,45; 17,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 23,01</t>
+          <t>10,3; 24,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 19,29</t>
+          <t>5,79; 19,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,68</t>
+          <t>0,88; 8,29</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 13,68</t>
+          <t>5,27; 13,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,83; 23,18</t>
+          <t>12,97; 23,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 16,92</t>
+          <t>7,5; 16,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 14,59</t>
+          <t>4,49; 14,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 14,86</t>
+          <t>6,59; 14,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 17,86</t>
+          <t>9,09; 18,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,27; 18,92</t>
+          <t>8,47; 19,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 9,37</t>
+          <t>2,99; 9,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,87; 12,81</t>
+          <t>6,53; 12,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,25; 19,08</t>
+          <t>12,03; 19,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,47; 16,29</t>
+          <t>9,13; 16,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,72; 9,94</t>
+          <t>4,51; 10,02</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>564; 5396</t>
+          <t>561; 5209</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3161; 11832</t>
+          <t>3090; 11748</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3454</t>
+          <t>0; 2898</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>562; 5399</t>
+          <t>555; 5172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1250; 7031</t>
+          <t>1307; 7365</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2501; 10294</t>
+          <t>2153; 9713</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1450; 8121</t>
+          <t>1505; 8271</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2961</t>
+          <t>0; 3320</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2267; 10046</t>
+          <t>2611; 10170</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6921; 18198</t>
+          <t>6780; 18020</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1510; 8893</t>
+          <t>1604; 9041</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>664; 6879</t>
+          <t>645; 6014</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2516; 8978</t>
+          <t>1969; 8886</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3024; 10609</t>
+          <t>2847; 10477</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4042; 11595</t>
+          <t>3914; 11626</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1244; 6910</t>
+          <t>1352; 7187</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1223; 6738</t>
+          <t>1247; 6951</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3313; 11984</t>
+          <t>3614; 12486</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1327; 7309</t>
+          <t>1325; 7555</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1780; 10083</t>
+          <t>1947; 11215</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4625; 13534</t>
+          <t>4547; 13402</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8250; 19745</t>
+          <t>8162; 19356</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6659; 16042</t>
+          <t>6632; 16025</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4323; 14857</t>
+          <t>4473; 14218</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>513; 4416</t>
+          <t>519; 5001</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2696; 9250</t>
+          <t>2753; 9042</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1062; 6441</t>
+          <t>1117; 6387</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1640; 17435</t>
+          <t>1870; 18198</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1803; 7876</t>
+          <t>1420; 7851</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>598; 5418</t>
+          <t>608; 5884</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3051; 10081</t>
+          <t>3016; 9953</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1461; 8144</t>
+          <t>1122; 8948</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2795; 9970</t>
+          <t>2785; 10224</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4152; 12589</t>
+          <t>4193; 12572</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5116; 13518</t>
+          <t>5151; 13927</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4772; 22101</t>
+          <t>5001; 21605</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>710; 5753</t>
+          <t>713; 5852</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4184; 13084</t>
+          <t>4581; 13227</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1692; 8255</t>
+          <t>1462; 8036</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>542; 5046</t>
+          <t>530; 4394</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1655; 8217</t>
+          <t>1426; 8459</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2759; 11056</t>
+          <t>2845; 11109</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>694; 5924</t>
+          <t>757; 6090</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3616</t>
+          <t>0; 3635</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2860; 11196</t>
+          <t>2869; 11322</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8936; 20483</t>
+          <t>9167; 22241</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3759; 12143</t>
+          <t>3643; 12019</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>568; 5588</t>
+          <t>564; 5339</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6445; 17141</t>
+          <t>6600; 17356</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18949; 34234</t>
+          <t>19150; 34373</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9846; 21561</t>
+          <t>9561; 20678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8044; 25937</t>
+          <t>7984; 25286</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9792; 21384</t>
+          <t>9481; 20949</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13999; 28216</t>
+          <t>14362; 29524</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10193; 23328</t>
+          <t>10447; 23916</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5777; 17076</t>
+          <t>5454; 16563</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18490; 34483</t>
+          <t>17591; 34355</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37430; 58313</t>
+          <t>36772; 58807</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23748; 40852</t>
+          <t>22883; 40249</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16992; 35777</t>
+          <t>16231; 36075</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A05-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A05-Habitat-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,83%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14,57%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16,11%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>21,67%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,48%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,11%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 15,87</t>
+          <t>4,44; 24,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 37,36</t>
+          <t>6,42; 27,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,9</t>
+          <t>6,26; 32,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 20,02</t>
+          <t>0,0; 13,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 25,69</t>
+          <t>1,76; 17,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,26; 28,21</t>
+          <t>10,24; 38,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 34,21</t>
+          <t>0,0; 12,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,0</t>
+          <t>1,93; 19,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 16,54</t>
+          <t>4,43; 17,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 27,36</t>
+          <t>10,89; 28,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 18,63</t>
+          <t>3,52; 18,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 11,24</t>
+          <t>1,25; 12,46</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8,21%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>12,29%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>14,44%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>16,58%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 21,34</t>
+          <t>3,0; 16,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 25,24</t>
+          <t>9,0; 29,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,17; 27,23</t>
+          <t>3,22; 18,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 16,24</t>
+          <t>3,42; 17,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 16,83</t>
+          <t>6,09; 22,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,96; 30,97</t>
+          <t>6,62; 24,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 18,36</t>
+          <t>9,16; 25,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 17,58</t>
+          <t>3,5; 17,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,48; 16,16</t>
+          <t>5,46; 16,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,98; 23,66</t>
+          <t>10,34; 24,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,91; 19,11</t>
+          <t>7,71; 19,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 13,16</t>
+          <t>4,38; 14,55</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11,02%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20,96%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>7,17%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>16,64%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10,87%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,22%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20,96%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 19,87</t>
+          <t>3,95; 21,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,35; 27,43</t>
+          <t>1,67; 15,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 23,13</t>
+          <t>11,33; 35,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 23,61</t>
+          <t>1,9; 13,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 22,35</t>
+          <t>2,04; 18,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 16,35</t>
+          <t>8,49; 28,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,85; 35,79</t>
+          <t>4,08; 22,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 15,72</t>
+          <t>4,67; 18,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 16,96</t>
+          <t>4,44; 16,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,08; 18,23</t>
+          <t>5,79; 17,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,29; 25,13</t>
+          <t>8,94; 24,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 16,12</t>
+          <t>4,3; 13,53</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12,89%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8,46%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>19,34%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>12,84%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,76%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 22,79</t>
+          <t>3,65; 21,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,96; 31,65</t>
+          <t>5,85; 22,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 24,51</t>
+          <t>2,35; 19,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 14,38</t>
+          <t>0,0; 9,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 21,79</t>
+          <t>2,77; 22,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 23,52</t>
+          <t>10,48; 31,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 20,2</t>
+          <t>5,79; 26,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,75</t>
+          <t>1,62; 15,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 17,55</t>
+          <t>5,31; 17,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,3; 24,99</t>
+          <t>10,32; 23,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 19,1</t>
+          <t>5,7; 18,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,29</t>
+          <t>0,94; 8,62</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>8,9%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>17,86%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>11,69%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 13,85</t>
+          <t>6,49; 15,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,97; 23,27</t>
+          <t>8,82; 18,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,5; 16,22</t>
+          <t>8,73; 18,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 14,23</t>
+          <t>2,82; 9,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 14,56</t>
+          <t>5,51; 13,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,09; 18,69</t>
+          <t>12,88; 23,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 19,4</t>
+          <t>7,52; 16,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 9,09</t>
+          <t>5,36; 12,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 12,76</t>
+          <t>6,83; 12,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,03; 19,24</t>
+          <t>12,25; 19,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,13; 16,05</t>
+          <t>9,44; 16,06</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 10,02</t>
+          <t>4,6; 9,34</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3391</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5016</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3894</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2060</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>6814</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3391</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5016</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3894</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2547</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>561; 5209</t>
+          <t>1274; 6960</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3090; 11748</t>
+          <t>2208; 9449</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2898</t>
+          <t>1512; 7928</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>555; 5172</t>
+          <t>0; 3259</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1307; 7365</t>
+          <t>578; 5600</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2153; 9713</t>
+          <t>3220; 12180</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1505; 8271</t>
+          <t>0; 3092</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3320</t>
+          <t>507; 5035</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2611; 10170</t>
+          <t>2726; 10487</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6780; 18020</t>
+          <t>7176; 18492</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1604; 9041</t>
+          <t>1710; 9033</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>645; 6014</t>
+          <t>634; 6347</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3243</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7076</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3593</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4634</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5119</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5992</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7079</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3483</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3243</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7076</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3593</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>7739</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1969; 8886</t>
+          <t>1240; 7019</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2847; 10477</t>
+          <t>3630; 11724</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3914; 11626</t>
+          <t>1327; 7562</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1352; 7187</t>
+          <t>1930; 9739</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1247; 6951</t>
+          <t>2535; 9331</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3614; 12486</t>
+          <t>2748; 10168</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1325; 7555</t>
+          <t>3911; 11072</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1947; 11215</t>
+          <t>1263; 6222</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4547; 13402</t>
+          <t>4532; 13685</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8162; 19356</t>
+          <t>8463; 20237</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6632; 16025</t>
+          <t>6462; 16393</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4473; 14218</t>
+          <t>4055; 13471</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3870</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2284</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5827</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3114</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1804</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>5487</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3003</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7874</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3870</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2284</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5827</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>8299</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>519; 5001</t>
+          <t>1388; 7699</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2753; 9042</t>
+          <t>601; 5507</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1117; 6387</t>
+          <t>3151; 9820</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1870; 18198</t>
+          <t>993; 7191</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1420; 7851</t>
+          <t>513; 4733</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>608; 5884</t>
+          <t>2799; 9474</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3016; 9953</t>
+          <t>1126; 6196</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1122; 8948</t>
+          <t>2373; 9493</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2785; 10224</t>
+          <t>2678; 10163</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4193; 12572</t>
+          <t>3990; 12210</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5151; 13927</t>
+          <t>4955; 13808</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5001; 21605</t>
+          <t>4438; 13955</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4178</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6089</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2744</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2173</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>8082</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4209</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1686</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4178</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6089</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2744</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2260</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>713; 5852</t>
+          <t>1418; 8273</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4581; 13227</t>
+          <t>2761; 10732</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1462; 8036</t>
+          <t>708; 6009</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>530; 4394</t>
+          <t>0; 3006</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1426; 8459</t>
+          <t>712; 5675</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2845; 11109</t>
+          <t>4381; 13190</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>757; 6090</t>
+          <t>1900; 8625</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3635</t>
+          <t>482; 4610</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2869; 11322</t>
+          <t>3428; 11316</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9167; 22241</t>
+          <t>9189; 21260</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3643; 12019</t>
+          <t>3588; 11945</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>564; 5339</t>
+          <t>576; 5276</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>14682</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20465</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16058</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8935</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>11155</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>26375</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>14895</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>15013</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>14682</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20465</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>16058</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>20846</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6600; 17356</t>
+          <t>9344; 21724</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19150; 34373</t>
+          <t>13930; 28618</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9561; 20678</t>
+          <t>10764; 23141</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7984; 25286</t>
+          <t>4658; 15696</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9481; 20949</t>
+          <t>6900; 17203</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14362; 29524</t>
+          <t>19018; 35328</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10447; 23916</t>
+          <t>9591; 21149</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5454; 16563</t>
+          <t>7662; 18239</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17591; 34355</t>
+          <t>18380; 33703</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36772; 58807</t>
+          <t>37446; 58597</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22883; 40249</t>
+          <t>23666; 40267</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16231; 36075</t>
+          <t>14164; 28753</t>
         </is>
       </c>
     </row>
